--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/close/close_annual_metrics.xlsx
@@ -468,16 +468,16 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.02062782764054583</v>
+        <v>0.025521819931553</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.001157844603912661</v>
+        <v>0.04833406932877971</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.3080464278423594</v>
+        <v>0.2629222056694968</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2768546848805925</v>
+        <v>0.2585043555886805</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.02848500430395779</v>
+        <v>0.1825134244790707</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.04090380559048961</v>
+        <v>0.2656526081302799</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.116980916692961</v>
+        <v>0.2769734497140123</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.2207914446180582</v>
+        <v>0.1750289405375366</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.2128189327169856</v>
+        <v>0.1849887605814738</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-0.1054339578690171</v>
+        <v>0.1650487736185735</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>18.43418072870808</v>
+        <v>13.59715212275173</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2363218694477649</v>
+        <v>-0.1606024137102819</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.01387412893235196</v>
+        <v>0.08390124430231038</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2115224105116187</v>
+        <v>0.1936492615519302</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1981779896699614</v>
+        <v>0.1913406145032397</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-1.29157426886377</v>
+        <v>-0.9214096383085457</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.741137982852444</v>
+        <v>-1.250271984909929</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-0.07025584595621637</v>
+        <v>0.4225106340088136</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2742915229688708</v>
+        <v>0.207058978574682</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1676480310388615</v>
+        <v>0.1140050048088755</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.8924179718737378</v>
+        <v>-0.8048575450202931</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>14.96801811934552</v>
+        <v>11.51481486034066</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1139378483481861</v>
+        <v>-0.1406918757324959</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.0002619762639113343</v>
+        <v>-0.02994023500824572</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2576932803392485</v>
+        <v>0.1574397454634359</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.234611372166492</v>
+        <v>0.1390407131176707</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.4186437234005831</v>
+        <v>-1.018479897498775</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.6161149328751596</v>
+        <v>-1.3674800299953</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.1027091599182101</v>
+        <v>-0.2040467418978988</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.2636103082829602</v>
+        <v>0.2036583752897778</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1463884870332844</v>
+        <v>0.07554289192142694</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.448980707040615</v>
+        <v>-0.7171771428301266</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>17.44690301178223</v>
+        <v>12.1961358938967</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1281328678173687</v>
+        <v>-0.005057614569599522</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.2283044683231126</v>
+        <v>-0.11936972415683</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2325229419601829</v>
+        <v>0.1994359546593547</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1675436379332564</v>
+        <v>0.1522816657454263</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.5619609847903504</v>
+        <v>-0.002706512949104248</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.7893349210171028</v>
+        <v>-0.00418419179905451</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.602709120088606</v>
+        <v>-0.9088071790816916</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2391896710980308</v>
+        <v>0.1852534802383301</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3240307749795958</v>
+        <v>0.2215685469251012</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.5562904741700297</v>
+        <v>-0.0284262172483544</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>16.62997474997207</v>
+        <v>12.8078266063296</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.4253381094539723</v>
+        <v>0.05618226587074648</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.1641872540590485</v>
+        <v>-0.1373317504567616</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.3387300506211924</v>
+        <v>0.1718532362148291</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2524722518700637</v>
+        <v>0.1201433884595554</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.210746624664494</v>
+        <v>0.3292549010871219</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.807853336137586</v>
+        <v>0.4426175208025211</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.7961110392519752</v>
+        <v>-1.269622908991059</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.2263763392057211</v>
+        <v>0.1111403952469705</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1996054884858924</v>
+        <v>0.2009181140226949</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.962090218896961</v>
+        <v>0.5247654918417693</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>18.47858854231917</v>
+        <v>13.77941447577021</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.09251633665565029</v>
+        <v>0.12332985445151</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1092003003393416</v>
+        <v>0.1404843755032004</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.449547388606635</v>
+        <v>0.3007194913430913</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3798323144075079</v>
+        <v>0.2730805264513934</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5517900678690791</v>
+        <v>0.8071450053616345</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.7601947911738869</v>
+        <v>1.126906781393077</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.6960428081000938</v>
+        <v>0.9486139692070403</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2556153538115975</v>
+        <v>0.148068285380764</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2329098019511113</v>
+        <v>0.1187260566845123</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.6860503964529897</v>
+        <v>1.597939885634429</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>19.35651143275181</v>
+        <v>14.09433063933378</v>
       </c>
     </row>
   </sheetData>
